--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -568,14 +568,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Prediction locked</t>
+          <t>No call</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>22520.45</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>22593.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.323</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>No call — not scored</t>
@@ -596,7 +600,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>No call. The S&amp;P move was 0.59%, under the 1% line.</t>
+          <t>No call. The S&amp;P move was 0.59%, under the 1% line. The open later moved 0.323% versus the previous close. This day is not counted.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap test" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gap test" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$2</definedName>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -585,8 +585,12 @@
           <t>No call — not scored</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>22363.35</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-1.017</v>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>No call — not scored</t>
@@ -609,8 +613,47 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q2"/>
+  <autoFilter ref="A1:Q3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -619,21 +619,41 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NO CALL</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>No call</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>22363.35</v>
+      </c>
+      <c r="H3" t="n">
+        <v>22364.15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.004</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -643,9 +663,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.698</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>No call. The S&amp;P move was -0.06%, under the 1% line. The open later moved 0.004% versus the previous close. This day is not counted.</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -656,11 +656,15 @@
           <t>No call — not scored</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>22721.95</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -680,8 +684,47 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q3"/>
+  <autoFilter ref="A1:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -690,21 +690,41 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-14 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NO CALL</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>No call</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>22721.95</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22715.75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.027</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -714,9 +734,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.604</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>No call. The S&amp;P move was -0.02%, under the 1% line. The open later moved -0.027% versus the previous close. This day is not counted.</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -727,11 +727,15 @@
           <t>No call — not scored</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>22622.7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.41</v>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -751,8 +755,47 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q4"/>
+  <autoFilter ref="A1:Q5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -761,21 +761,41 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>Gap scored</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>22622.7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>22671.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.215</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Opposite</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -785,9 +805,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.437</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>The opening gap went the other way (0.215%). The call used only the S&amp;P move of -1.11% and did not see the Indian open. The US move was only just past 1%. Days like this stay in the sheet so a later review can see whether small moves miss more often. One day does not change the rule. India VIX known before the open was 14.63. NIFTY's previous session moved -0.437%.</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -781,7 +781,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gap scored</t>
+          <t>Day scored</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -798,11 +798,15 @@
           <t>Opposite</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>22997.35</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.438</v>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Opposite</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -813,7 +817,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>The opening gap went the other way (0.215%). The call used only the S&amp;P move of -1.11% and did not see the Indian open. The US move was only just past 1%. Days like this stay in the sheet so a later review can see whether small moves miss more often. One day does not change the rule. India VIX known before the open was 14.63. NIFTY's previous session moved -0.437%.</t>
+          <t>The opening gap went the other way (0.215%). The call used only the S&amp;P move of -1.11% and did not see the Indian open. After the open, the session went the other way (1.438%). The rule is about the gap, so this is recorded separately and does not rewrite the call. The US move was only just past 1%. Days like this stay in the sheet so a later review can see whether small moves miss more often. One day does not change the rule. India VIX known before the open was 14.63. NIFTY's previous session moved -0.437%.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -822,8 +826,47 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q5"/>
+  <autoFilter ref="A1:Q6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -832,21 +832,41 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NO CALL</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>No call</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>22997.35</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23065.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.295</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -856,9 +876,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>No call. The S&amp;P move was 0.33%, under the 1% line. The open later moved 0.295% versus the previous close. This day is not counted.</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -869,11 +869,15 @@
           <t>No call — not scored</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>23146.15</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.351</v>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -893,8 +897,47 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q6"/>
+  <autoFilter ref="A1:Q7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -903,21 +903,41 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+          <t>Gap scored</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>23146.15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23150.85</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.02</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Opposite</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -927,9 +947,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>The opening gap went the other way (0.02%). The call used only the S&amp;P move of -1.09% and did not see the Indian open. The US move was only just past 1%. Days like this stay in the sheet so a later review can see whether small moves miss more often. One day does not change the rule. India VIX known before the open was 14.06. NIFTY's previous session moved 0.647%.</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -923,7 +923,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gap scored</t>
+          <t>Day scored</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -940,11 +940,15 @@
           <t>Opposite</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>22888.95</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1.131</v>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Same way</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -955,7 +959,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>The opening gap went the other way (0.02%). The call used only the S&amp;P move of -1.09% and did not see the Indian open. The US move was only just past 1%. Days like this stay in the sheet so a later review can see whether small moves miss more often. One day does not change the rule. India VIX known before the open was 14.06. NIFTY's previous session moved 0.647%.</t>
+          <t>The opening gap went the other way (0.02%). The call used only the S&amp;P move of -1.09% and did not see the Indian open. After the open, the session also went the same way (-1.131%). The US move was only just past 1%. Days like this stay in the sheet so a later review can see whether small moves miss more often. One day does not change the rule. India VIX known before the open was 14.06. NIFTY's previous session moved 0.647%.</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -964,8 +968,47 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q7"/>
+  <autoFilter ref="A1:Q8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -974,21 +974,41 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-21 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NO CALL</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>No call</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>22888.95</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23016</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.555</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -998,9 +1018,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-1.111</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>No call. The S&amp;P move was 0.28%, under the 1% line. The open later moved 0.555% versus the previous close. This day is not counted.</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1011,11 +1011,15 @@
           <t>No call — not scored</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>22811.35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.889</v>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1035,8 +1039,47 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q8"/>
+  <autoFilter ref="A1:Q9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -1045,21 +1045,41 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-22 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NO CALL</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>No call</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>22811.35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>22687.75</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.542</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1069,9 +1089,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.339</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>No call. The S&amp;P move was 0.58%, under the 1% line. The open later moved -0.542% versus the previous close. This day is not counted.</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1082,11 +1082,15 @@
           <t>No call — not scored</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>22687.65</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0</v>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1106,8 +1110,47 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q9"/>
+  <autoFilter ref="A1:Q10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -1116,21 +1116,41 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Gap scored</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>22687.65</v>
+      </c>
+      <c r="H10" t="n">
+        <v>22742.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.24</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Opposite</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1140,9 +1160,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.542</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>The opening gap went the other way (0.24%). The call used only the S&amp;P move of -1.21% and did not see the Indian open. The US move was only just past 1%. Days like this stay in the sheet so a later review can see whether small moves miss more often. One day does not change the rule. India VIX known before the open was 15.76. NIFTY's previous session moved -0.542%.</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gap scored</t>
+          <t>Day scored</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1153,11 +1153,15 @@
           <t>Opposite</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>22600</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.625</v>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Same way</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1168,7 +1172,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>The opening gap went the other way (0.24%). The call used only the S&amp;P move of -1.21% and did not see the Indian open. The US move was only just past 1%. Days like this stay in the sheet so a later review can see whether small moves miss more often. One day does not change the rule. India VIX known before the open was 15.76. NIFTY's previous session moved -0.542%.</t>
+          <t>The opening gap went the other way (0.24%). The call used only the S&amp;P move of -1.21% and did not see the Indian open. After the open, the session also went the same way (-0.625%). The US move was only just past 1%. Days like this stay in the sheet so a later review can see whether small moves miss more often. One day does not change the rule. India VIX known before the open was 15.76. NIFTY's previous session moved -0.542%.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1177,8 +1181,47 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q10"/>
+  <autoFilter ref="A1:Q11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -1187,21 +1187,41 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NO CALL</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>No call</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>22600</v>
+      </c>
+      <c r="H11" t="n">
+        <v>22524.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.335</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1211,9 +1231,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.386</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>No call. The S&amp;P move was -0.52%, under the 1% line. The open later moved -0.335% versus the previous close. This day is not counted.</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1224,11 +1224,15 @@
           <t>No call — not scored</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>22753.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.016</v>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1248,8 +1252,47 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q11"/>
+  <autoFilter ref="A1:Q12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -1258,21 +1258,41 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-27 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NO CALL</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>No call</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>22753.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>22708.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.195</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1282,9 +1302,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>No call. The S&amp;P move was 0.7%, under the 1% line. The open later moved -0.195% versus the previous close. This day is not counted.</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1295,11 +1295,15 @@
           <t>No call — not scored</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>22749.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.18</v>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1319,8 +1323,47 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -1329,21 +1329,41 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NO CALL</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+          <t>No call</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>22749.75</v>
+      </c>
+      <c r="H13" t="n">
+        <v>22678</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.315</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1353,9 +1373,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>No call. The S&amp;P move was 0.6%, under the 1% line. The open later moved -0.315% versus the previous close. This day is not counted.</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1366,11 +1366,15 @@
           <t>No call — not scored</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>22698.85</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.092</v>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1390,8 +1394,47 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q13"/>
+  <autoFilter ref="A1:Q14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -1400,21 +1400,41 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-29 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NO CALL</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+          <t>No call</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>22698.85</v>
+      </c>
+      <c r="H14" t="n">
+        <v>22690.65</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.036</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1424,9 +1444,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.224</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>No call. The S&amp;P move was 0.28%, under the 1% line. The open later moved -0.036% versus the previous close. This day is not counted.</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1437,11 +1437,15 @@
           <t>No call — not scored</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>22936.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.085</v>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1461,8 +1465,47 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q14"/>
+  <autoFilter ref="A1:Q15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -1471,21 +1471,41 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-30 08:00 IST</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NO CALL</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waiting for US data</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>No call</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>22936.75</v>
+      </c>
+      <c r="H15" t="n">
+        <v>22964.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.121</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1495,9 +1515,17 @@
           <t>Waiting</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>No call. The S&amp;P move was -0.3%, under the 1% line. The open later moved 0.121% versus the previous close. This day is not counted.</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>

--- a/live_log/nifty_gap_log.xlsx
+++ b/live_log/nifty_gap_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap test'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1508,11 +1508,15 @@
           <t>No call — not scored</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>23053.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.386</v>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>No call — not scored</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1532,8 +1536,47 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Waiting for US data</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>The call uses the completed US session only. Indian prices are filled afterwards and are not used to choose the call.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q15"/>
+  <autoFilter ref="A1:Q16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
